--- a/tools/importer/reports/import-company-hub.report.xlsx
+++ b/tools/importer/reports/import-company-hub.report.xlsx
@@ -52,7 +52,7 @@
     <t>company-hub</t>
   </si>
   <si>
-    <t>2026-03-06T14:40:04.739Z</t>
+    <t>2026-03-06T14:59:38.007Z</t>
   </si>
   <si>
     <t>Our Company | About UPS</t>
@@ -73,7 +73,7 @@
     <t>story-hub</t>
   </si>
   <si>
-    <t>2026-03-06T14:39:42.372Z</t>
+    <t>2026-03-06T14:59:29.310Z</t>
   </si>
   <si>
     <t>Our Stories | About UPS</t>
@@ -94,7 +94,7 @@
     <t>company-culture</t>
   </si>
   <si>
-    <t>2026-03-06T14:21:19.704Z</t>
+    <t>2026-03-06T14:40:11.991Z</t>
   </si>
   <si>
     <t>Our Culture</t>
@@ -115,7 +115,7 @@
     <t>company-strategy</t>
   </si>
   <si>
-    <t>2026-03-06T14:21:12.153Z</t>
+    <t>2026-03-06T14:40:08.818Z</t>
   </si>
   <si>
     <t>Our Strategy | About UPS</t>
